--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORTO_PLAZO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORTO_PLAZO.xlsx
@@ -2606,11 +2606,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="88654094"/>
-        <c:axId val="20006956"/>
+        <c:axId val="14506182"/>
+        <c:axId val="89202774"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="88654094"/>
+        <c:axId val="14506182"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2644,7 +2644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20006956"/>
+        <c:crossAx val="89202774"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2656,7 +2656,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="20006956"/>
+        <c:axId val="89202774"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2699,7 +2699,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="88654094"/>
+        <c:crossAx val="14506182"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3593,11 +3593,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="90149895"/>
-        <c:axId val="13184261"/>
+        <c:axId val="48227005"/>
+        <c:axId val="28722199"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90149895"/>
+        <c:axId val="48227005"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3629,14 +3629,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13184261"/>
+        <c:crossAx val="28722199"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="13184261"/>
+        <c:axId val="28722199"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="80"/>
@@ -3676,7 +3676,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90149895"/>
+        <c:crossAx val="48227005"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="AW20" s="33" t="n">
         <f aca="false">LOOKUP(AW19,$A$3:$A$2973,$B$3:$B$2973)</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="AX20" s="33" t="n">
         <f aca="false">LOOKUP(AX19,$A$3:$A$2973,$B$3:$B$2973)</f>
@@ -7913,7 +7913,7 @@
       </c>
       <c r="AH22" s="22" t="n">
         <f aca="false">+S23/R23-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI22" s="9"/>
       <c r="AJ22" s="9"/>
@@ -7925,7 +7925,7 @@
       <c r="AP22" s="9"/>
       <c r="AQ22" s="23" t="n">
         <f aca="false">+(S23/P23-1)/COUNTA(AE22:AP22)*12</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="AV22" s="28" t="s">
         <v>27</v>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="S23" s="20" t="n">
         <f aca="false">+B249</f>
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="U23" s="19"/>
       <c r="Y23" s="19"/>
@@ -8477,23 +8477,23 @@
       </c>
       <c r="AX29" s="43" t="n">
         <f aca="false">$AW20/AX20-1</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AY29" s="43" t="n">
         <f aca="false">$AW20/AY20-1</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="AZ29" s="43" t="n">
         <f aca="false">$AW20/AZ20-1</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="BA29" s="43" t="n">
         <f aca="false">$AW20/BA20-1</f>
-        <v>-0.220741912237796</v>
+        <v>-0.209569757039683</v>
       </c>
       <c r="BB29" s="43" t="n">
         <f aca="false">+AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
       <c r="BC29" s="44"/>
       <c r="BD29" s="27"/>
@@ -12547,7 +12547,7 @@
       </c>
       <c r="AH86" s="60" t="n">
         <f aca="false">+AH22</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="AI86" s="60"/>
       <c r="AJ86" s="60"/>
@@ -12559,7 +12559,7 @@
       <c r="AP86" s="60"/>
       <c r="AQ86" s="60" t="n">
         <f aca="false">+AQ22</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="87" s="4" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -18096,15 +18096,15 @@
         <v>46142</v>
       </c>
       <c r="B249" s="3" t="n">
-        <v>19635.3400812264</v>
+        <v>19916.8502383877</v>
       </c>
       <c r="C249" s="25" t="n">
         <f aca="false">(B249/B248-1)/(A249-A248)*30</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="D249" s="19" t="n">
         <f aca="false">+D248*(1+C249)</f>
-        <v>87.6287018826645</v>
+        <v>88.8850269341679</v>
       </c>
       <c r="F249" s="17" t="n">
         <v>46142</v>
@@ -18231,20 +18231,20 @@
       </c>
       <c r="T2" s="84" t="n">
         <f aca="false">+'Datos ICP (2)'!AX29</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="U2" s="84" t="n">
         <f aca="false">+'Datos ICP (2)'!AY29</f>
-        <v>-0.248750231235289</v>
+        <v>-0.237979628862347</v>
       </c>
       <c r="V2" s="84" t="n">
         <f aca="false">+'Datos ICP (2)'!AZ29</f>
-        <v>-0.239809516977627</v>
+        <v>-0.228910732364632</v>
       </c>
       <c r="W2" s="84"/>
       <c r="X2" s="84" t="n">
         <f aca="false">+'Datos ICP (2)'!BB29</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19558,7 +19558,7 @@
       </c>
       <c r="H39" s="99" t="n">
         <f aca="false">+'Datos ICP (2)'!AH86</f>
-        <v>-0.254362857499898</v>
+        <v>-0.243672722859896</v>
       </c>
       <c r="I39" s="99"/>
       <c r="J39" s="99"/>
@@ -19570,7 +19570,7 @@
       <c r="P39" s="99"/>
       <c r="Q39" s="99" t="n">
         <f aca="false">+'Datos ICP (2)'!AQ86</f>
-        <v>-0.746250693705866</v>
+        <v>-0.71393888658704</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORTO_PLAZO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORTO_PLAZO.xlsx
@@ -2606,11 +2606,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="14506182"/>
-        <c:axId val="89202774"/>
+        <c:axId val="26112882"/>
+        <c:axId val="81156538"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="14506182"/>
+        <c:axId val="26112882"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2644,7 +2644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89202774"/>
+        <c:crossAx val="81156538"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2656,7 +2656,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="89202774"/>
+        <c:axId val="81156538"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2699,7 +2699,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14506182"/>
+        <c:crossAx val="26112882"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3593,11 +3593,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="48227005"/>
-        <c:axId val="28722199"/>
+        <c:axId val="14358810"/>
+        <c:axId val="90512763"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="48227005"/>
+        <c:axId val="14358810"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3629,14 +3629,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="28722199"/>
+        <c:crossAx val="90512763"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="28722199"/>
+        <c:axId val="90512763"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="80"/>
@@ -3676,7 +3676,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48227005"/>
+        <c:crossAx val="14358810"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORTO_PLAZO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORTO_PLAZO.xlsx
@@ -2606,11 +2606,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="26112882"/>
-        <c:axId val="81156538"/>
+        <c:axId val="64550967"/>
+        <c:axId val="32906634"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="26112882"/>
+        <c:axId val="64550967"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2644,7 +2644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81156538"/>
+        <c:crossAx val="32906634"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2656,7 +2656,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="81156538"/>
+        <c:axId val="32906634"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2699,7 +2699,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26112882"/>
+        <c:crossAx val="64550967"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3593,11 +3593,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="14358810"/>
-        <c:axId val="90512763"/>
+        <c:axId val="43957001"/>
+        <c:axId val="37996536"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="14358810"/>
+        <c:axId val="43957001"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3629,14 +3629,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90512763"/>
+        <c:crossAx val="37996536"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="90512763"/>
+        <c:axId val="37996536"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="80"/>
@@ -3676,7 +3676,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14358810"/>
+        <c:crossAx val="43957001"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>

--- a/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORTO_PLAZO.xlsx
+++ b/inputs/templates/TEMPLATE_FONDO_LIQUIDEZ_CORTO_PLAZO.xlsx
@@ -2606,11 +2606,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="64550967"/>
-        <c:axId val="32906634"/>
+        <c:axId val="38660588"/>
+        <c:axId val="25708031"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="64550967"/>
+        <c:axId val="38660588"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="43373"/>
@@ -2644,7 +2644,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32906634"/>
+        <c:crossAx val="25708031"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
@@ -2656,7 +2656,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="32906634"/>
+        <c:axId val="25708031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="100"/>
@@ -2699,7 +2699,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64550967"/>
+        <c:crossAx val="38660588"/>
         <c:crossesAt val="38687"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3593,11 +3593,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="43957001"/>
-        <c:axId val="37996536"/>
+        <c:axId val="67637546"/>
+        <c:axId val="99835694"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="43957001"/>
+        <c:axId val="67637546"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3629,14 +3629,14 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="37996536"/>
+        <c:crossAx val="99835694"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
         <c:noMultiLvlLbl val="0"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="37996536"/>
+        <c:axId val="99835694"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="80"/>
@@ -3676,7 +3676,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43957001"/>
+        <c:crossAx val="67637546"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
         <c:majorUnit val="10"/>
